--- a/output/pdf_financials_xlsx/AD.UN.xlsx
+++ b/output/pdf_financials_xlsx/AD.UN.xlsx
@@ -4762,34 +4762,34 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>9.766188</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>2167.992</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>-3682.068</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>2071.469</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>4434.065</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-3682.068</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>0.015052</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>0.051391</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>0.033711</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>0.033711</v>
       </c>
       <c r="N91" s="3" t="n">
         <v>0</v>
@@ -10043,7 +10043,11 @@
           <t>Translation reserve</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -13018,7 +13022,11 @@
           <t>Fair value reserve</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -20404,7 +20412,11 @@
           <t>Fair value reserve 2,292,939</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AD.UN.xlsx
+++ b/output/pdf_financials_xlsx/AD.UN.xlsx
@@ -2058,13 +2058,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.743936</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.826</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.816868</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>3888.465</v>
@@ -2082,19 +2082,19 @@
         <v>8998.342000000001</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.018447</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.060193</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.015184</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.004198</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.006385</v>
       </c>
     </row>
     <row r="35">
@@ -2150,13 +2150,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.743936</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.826</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.816868</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>3888.465</v>
@@ -2174,19 +2174,19 @@
         <v>8998.342000000001</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.018447</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.060193</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.015184</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.004198</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.006385</v>
       </c>
     </row>
     <row r="37">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>5.579627</v>
+        <v>3.835691</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>6.925472</v>
+        <v>3.099472</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.929472</v>
+        <v>2.112604</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>119.508</v>
@@ -2726,16 +2726,16 @@
         <v>8625.543</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.064245</v>
+        <v>0.045798</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.088064</v>
+        <v>0.027871</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.048272</v>
+        <v>0.033088</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.048272</v>
+        <v>0.044074</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0</v>
@@ -6327,19 +6327,19 @@
         </is>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.000159</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.000148</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.000144</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.000203</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.000154</v>
       </c>
     </row>
     <row r="125">
@@ -6375,19 +6375,19 @@
         </is>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000159</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000148</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000144</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000203</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000154</v>
       </c>
     </row>
     <row r="126">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -20809,7 +20809,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E180" s="5" t="n">
@@ -24382,7 +24382,11 @@
           <t>Office lease payments</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AD.UN.xlsx
+++ b/output/pdf_financials_xlsx/AD.UN.xlsx
@@ -903,19 +903,19 @@
         <v>11.593153</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.531381</v>
+        <v>12.520048</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>47398.393</v>
+        <v>43860.074</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>30309.74</v>
+        <v>25998.663</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>46915.666</v>
+        <v>40134.886</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>63053.699</v>
+        <v>54133.067</v>
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
@@ -923,19 +923,19 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.21489</v>
+        <v>0.191798</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.198081</v>
+        <v>0.168431</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.241251</v>
+        <v>0.20243</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.154989</v>
+        <v>0.128965</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.176701</v>
+        <v>0.151319</v>
       </c>
     </row>
     <row r="12">
@@ -5679,19 +5679,19 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.011989</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-12.979</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-9.835000000000001</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-15.29</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-69.34</v>
       </c>
       <c r="I111" s="1" t="inlineStr">
         <is>
@@ -5843,16 +5843,16 @@
         </is>
       </c>
       <c r="J114" s="3" t="n">
-        <v>0</v>
+        <v>-0.35775</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>-0.155884</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>0</v>
+        <v>-0.130103</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>0</v>
+        <v>-0.130103</v>
       </c>
       <c r="N114" s="3" t="n">
         <v>0</v>
@@ -6815,19 +6815,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.011989</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-12.979</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-9.835000000000001</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-15.29</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-69.34</v>
       </c>
       <c r="I134" s="1" t="inlineStr">
         <is>
@@ -6867,19 +6867,19 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>12.377495</v>
+        <v>12.365506</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>14610.092</v>
+        <v>14597.113</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>26463.749</v>
+        <v>26453.914</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>43745.944</v>
+        <v>43730.654</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>49647.62</v>
+        <v>49578.28</v>
       </c>
       <c r="I135" s="1" t="inlineStr">
         <is>
@@ -22948,7 +22948,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -23896,7 +23900,11 @@
           <t>Cash generated from / (used in) operating activities $</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -25899,7 +25907,11 @@
           <t>Cash generated from operating activities $</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -26636,7 +26648,11 @@
           <t>Deferred income tax expense 17</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -27426,7 +27442,11 @@
           <t>Cash generated from operating activities $</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -27669,7 +27689,11 @@
           <t>Acquisition of investments 3 $</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -28305,7 +28329,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -28933,7 +28961,11 @@
           <t>Acquisition of investments 5 $</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -30126,7 +30158,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -30371,7 +30407,11 @@
           <t>Acquisition of investments 5</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -31416,7 +31456,11 @@
           <t>Deferred income tax expense 6</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -32437,7 +32481,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>-</t>
@@ -32660,7 +32708,11 @@
           <t>Acquisition of equipment 7</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -34052,7 +34104,11 @@
           <t>Deferred income tax expense 6</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -36701,7 +36757,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
@@ -39660,7 +39720,11 @@
           <t>Earnings from operations $</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -40136,7 +40200,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
@@ -41432,7 +41500,11 @@
           <t>Earnings from operations $</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E439" t="inlineStr">
         <is>
           <t>-</t>
@@ -41930,7 +42002,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E445" t="inlineStr">
         <is>
           <t>-</t>
@@ -45961,7 +46037,11 @@
           <t>Earnings from operations</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr">
         <is>
           <t>-</t>
@@ -48311,7 +48391,11 @@
           <t>Earnings from operations</t>
         </is>
       </c>
-      <c r="D526" t="inlineStr"/>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E526" t="inlineStr">
         <is>
           <t>-</t>
